--- a/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
@@ -1799,13 +1799,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2BEE0DC-9104-42E1-9F6B-0E4E5B80D33F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F9F646A-F433-4D80-AAAF-6F31A53535A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08212D12-B1CF-4CC9-8D81-A2ADE0980586}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27573064-16B2-4CA6-B9EC-98BED125BE47}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D41567-1983-46AB-8FFE-5E11D5AA17B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAD6784-70BE-4148-ADB7-5D06B052F741}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
@@ -1799,13 +1799,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F9F646A-F433-4D80-AAAF-6F31A53535A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00CD757-71BB-48F3-8669-3A8195203EC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27573064-16B2-4CA6-B9EC-98BED125BE47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CE49CD-4A1A-4E7F-B34B-A193FC97677E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAD6784-70BE-4148-ADB7-5D06B052F741}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EA2D3D6-4A0A-4A2D-9C39-DE7C9C61EDD9}"/>
 </file>
--- a/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
+++ b/ksoft_old/docs/records/Sales_Operation_Types_Records.xlsx
@@ -1799,13 +1799,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00CD757-71BB-48F3-8669-3A8195203EC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2BEE0DC-9104-42E1-9F6B-0E4E5B80D33F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CE49CD-4A1A-4E7F-B34B-A193FC97677E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08212D12-B1CF-4CC9-8D81-A2ADE0980586}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EA2D3D6-4A0A-4A2D-9C39-DE7C9C61EDD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D41567-1983-46AB-8FFE-5E11D5AA17B7}"/>
 </file>